--- a/Lineaire Regressie logboek.xlsx
+++ b/Lineaire Regressie logboek.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serza\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serza\Documents\GitHub\DEAI-Serzat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78989326-8771-45D2-99DD-9326BC8B3BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D6DC84-971A-4529-AF89-1D9D28D8F31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,87 +25,260 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
-  <si>
-    <t>Target Variabele</t>
-  </si>
-  <si>
-    <t>Experiment</t>
-  </si>
-  <si>
-    <t>Gebruikte Features</t>
-  </si>
-  <si>
-    <t>Hyperparameter 1 (max_iter)</t>
-  </si>
-  <si>
-    <t>Hyperparameter 2 (eta0)</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>R-squared (R2)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>Initiële Run</t>
   </si>
   <si>
-    <t>SalePrice</t>
-  </si>
-  <si>
-    <t>Overall Qual, Gr Liv Area, Neighborhood</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>42578.28</t>
-  </si>
-  <si>
     <t>0.7567</t>
   </si>
   <si>
-    <t>Experiment 1</t>
-  </si>
-  <si>
-    <t>Overall Qual, Gr Liv Area, Neighborhood, Total Bsmt SF, Garage, House Style</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>42646.60</t>
-  </si>
-  <si>
     <t>0.7559</t>
   </si>
   <si>
-    <t>Experiment 2</t>
-  </si>
-  <si>
-    <t>Overall Qual, Gr Liv Area, Total Bsmt SF, Year Built</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>48187.95</t>
-  </si>
-  <si>
     <t>0.6884</t>
   </si>
   <si>
-    <t>Experiment 3</t>
-  </si>
-  <si>
-    <t>Overall Qual, Gr Liv Area, Neighborhood, Year Built, Full Bath</t>
-  </si>
-  <si>
-    <t>42791.79</t>
-  </si>
-  <si>
     <t>0.7542</t>
+  </si>
+  <si>
+    <t>Exp #</t>
+  </si>
+  <si>
+    <t>Belangrijkste Features</t>
+  </si>
+  <si>
+    <t>Algoritme &amp; Instellingen</t>
+  </si>
+  <si>
+    <t>R2 Score</t>
+  </si>
+  <si>
+    <t>Qual, Area, Neighborhood</t>
+  </si>
+  <si>
+    <t>SGDRegressor (Standard)</t>
+  </si>
+  <si>
+    <t>Basispunt voor verdere experimenten.</t>
+  </si>
+  <si>
+    <t>Meer features toevoegen</t>
+  </si>
+  <si>
+    <t>+Bsmt, +Garage, +Style</t>
+  </si>
+  <si>
+    <t>SGD (5000 iter, lr 0.001)</t>
+  </si>
+  <si>
+    <t>Meer features hielpen niet direct de score te verhogen.</t>
+  </si>
+  <si>
+    <t>Alleen Numerieke data</t>
+  </si>
+  <si>
+    <t>Qual, Area, Bsmt, Year</t>
+  </si>
+  <si>
+    <t>SGD (Constant LR 0.005)</t>
+  </si>
+  <si>
+    <t>De locatie (Neighborhood) is essentieel voor de prijs.</t>
+  </si>
+  <si>
+    <t>Gemixte features</t>
+  </si>
+  <si>
+    <t>Qual, Area, Neigh, Year, Bath</t>
+  </si>
+  <si>
+    <t>SGD (500 iter, lr 0.01)</t>
+  </si>
+  <si>
+    <t>De balans tussen numeriek en categorisch is stabieler.</t>
+  </si>
+  <si>
+    <t>Ridge met alle data</t>
+  </si>
+  <si>
+    <t>Alle kolommen (drop ID/Price)</t>
+  </si>
+  <si>
+    <t>Ridge Regression (alpha 10)</t>
+  </si>
+  <si>
+    <t>0.7413</t>
+  </si>
+  <si>
+    <t>Ridge is stabieler bij een grote hoeveelheid variabelen.</t>
+  </si>
+  <si>
+    <t>L1 Regularisatie</t>
+  </si>
+  <si>
+    <t>Mix (Exp 3)</t>
+  </si>
+  <si>
+    <t>SGDRegressor (Penalty='l1')</t>
+  </si>
+  <si>
+    <t>L1 helpt bij feature selectie, maar score bleef gelijk.</t>
+  </si>
+  <si>
+    <t>Feature Engineering</t>
+  </si>
+  <si>
+    <t>House_Age (2024 - Year)</t>
+  </si>
+  <si>
+    <t>SGDRegressor</t>
+  </si>
+  <si>
+    <t>0.6878</t>
+  </si>
+  <si>
+    <t>Leeftijd alleen is minder sterk dan het bouwjaar zelf.</t>
+  </si>
+  <si>
+    <t>Alternatieve Scaling</t>
+  </si>
+  <si>
+    <t>MinMaxScaler</t>
+  </si>
+  <si>
+    <t>0.7641</t>
+  </si>
+  <si>
+    <t>MinMaxScaler presteerde iets beter dan StandardScaler.</t>
+  </si>
+  <si>
+    <t>Finaal Ridge Model</t>
+  </si>
+  <si>
+    <t>Beste selectie (Top 7)</t>
+  </si>
+  <si>
+    <t>Ridge Regression</t>
+  </si>
+  <si>
+    <t>0.7447</t>
+  </si>
+  <si>
+    <t>Zeer stabiel model, maar lineair verband is beperkt.</t>
+  </si>
+  <si>
+    <t>Polynomial Features</t>
+  </si>
+  <si>
+    <t>Finaal selectie (Degree 2)</t>
+  </si>
+  <si>
+    <t>Ridge + Poly</t>
+  </si>
+  <si>
+    <t>0.9013</t>
+  </si>
+  <si>
+    <r>
+      <t>Beste resultaat!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Er zijn kwadratische relaties.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lasso Regression</t>
+  </si>
+  <si>
+    <t>Finaal selectie</t>
+  </si>
+  <si>
+    <t>Lasso (alpha 100)</t>
+  </si>
+  <si>
+    <t>0.7442</t>
+  </si>
+  <si>
+    <t>Lasso negeert onbelangrijke features automatisch.</t>
+  </si>
+  <si>
+    <t>ElasticNet</t>
+  </si>
+  <si>
+    <t>ElasticNet (Mix L1/L2)</t>
+  </si>
+  <si>
+    <t>0.7501</t>
+  </si>
+  <si>
+    <t>Goede balans, maar Ridge/Lasso apart zijn duidelijker.</t>
+  </si>
+  <si>
+    <t>Decision Tree</t>
+  </si>
+  <si>
+    <t>DecisionTreeRegressor</t>
+  </si>
+  <si>
+    <t>0.8502</t>
+  </si>
+  <si>
+    <t>Niet-lineaire modellen werken erg goed op deze data.</t>
+  </si>
+  <si>
+    <t>Random Forest</t>
+  </si>
+  <si>
+    <t>Finaal selectie (100 bomen)</t>
+  </si>
+  <si>
+    <t>RandomForestRegressor</t>
+  </si>
+  <si>
+    <t>0.8865</t>
+  </si>
+  <si>
+    <t>Zeer krachtig model door combinatie van bomen.</t>
+  </si>
+  <si>
+    <t>Cross-Validation</t>
+  </si>
+  <si>
+    <t>Alle data</t>
+  </si>
+  <si>
+    <t>Ridge (5-Fold CV)</t>
+  </si>
+  <si>
+    <t>0.8155</t>
+  </si>
+  <si>
+    <t>Het model is betrouwbaar over de hele dataset.</t>
+  </si>
+  <si>
+    <t>Log-Transformation</t>
+  </si>
+  <si>
+    <t>Ridge + Log(y)</t>
+  </si>
+  <si>
+    <t>0.0776</t>
+  </si>
+  <si>
+    <t>Log-transform werkte niet goed op de testset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omschrijving </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusie </t>
   </si>
 </sst>
 </file>
@@ -140,12 +313,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -175,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -187,6 +372,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -469,131 +675,355 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="73.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="D3" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="72" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3">
-        <v>500</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
+      <c r="B17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
